--- a/data/trans_bre/IQ2601_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ2601_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,88</t>
+          <t>11,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 15,67</t>
+          <t>-8,59; 15,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 18,76</t>
+          <t>-5,94; 17,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 15,77</t>
+          <t>-11,04; 17,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 48,99</t>
+          <t>-19,62; 39,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 26,05</t>
+          <t>-11,92; 26,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 57,06</t>
+          <t>-13,01; 54,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 28,07</t>
+          <t>-16,1; 32,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 112,75</t>
+          <t>-22,75; 85,13</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,76</t>
+          <t>-6,71</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,95%</t>
+          <t>-9,29%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 7,33</t>
+          <t>-2,47; 7,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 6,69</t>
+          <t>-4,12; 6,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 4,55</t>
+          <t>-5,52; 4,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 4,89</t>
+          <t>-17,12; 4,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 11,96</t>
+          <t>-3,73; 12,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 14,32</t>
+          <t>-8,03; 13,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 7,35</t>
+          <t>-8,08; 7,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 6,9</t>
+          <t>-23,15; 6,76</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,54</t>
+          <t>-6,95</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-7,17%</t>
+          <t>-8,93%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 8,86</t>
+          <t>-7,39; 8,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 17,8</t>
+          <t>-0,74; 18,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 6,84</t>
+          <t>-9,72; 6,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 11,85</t>
+          <t>-22,0; 11,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 13,16</t>
+          <t>-9,75; 12,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 37,11</t>
+          <t>-1,35; 36,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 11,74</t>
+          <t>-14,61; 11,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 18,16</t>
+          <t>-26,35; 16,62</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,45</t>
+          <t>-5,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-4,72%</t>
+          <t>-7,24%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 6,37</t>
+          <t>-1,62; 6,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 7,77</t>
+          <t>-0,69; 7,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,77</t>
+          <t>-4,12; 4,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 4,71</t>
+          <t>-14,2; 3,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 10,11</t>
+          <t>-2,4; 10,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 16,72</t>
+          <t>-1,26; 16,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,97</t>
+          <t>-6,23; 6,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 6,9</t>
+          <t>-18,36; 5,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2601_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ2601_R2-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,47</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,02</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,49</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.468389938689309</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.022746369198867</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.45178132439785</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>11.48934902380688</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.05315677402939995</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1519022693422954</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.03935797270994369</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1665751627422217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,59; 15,32</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,94; 17,92</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-11,04; 17,36</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-19,62; 39,93</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-11,92; 26,85</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-13,01; 54,52</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-16,1; 32,39</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-22,75; 85,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.58602247959452</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.939606871513724</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-11.04287430676686</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-19.61609040414174</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1192423768721368</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1300824926224633</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1609818467284502</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2275201304123745</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>15.31690549357825</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>17.9216260660787</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>17.35751969559593</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>39.93205940405669</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.2684669568985697</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.5452143305840591</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.3239262259530892</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.8513232065847488</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,42</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,71</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-0,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-9,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,47; 7,77</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 6,42</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,52; 4,73</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-17,12; 4,62</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-3,73; 12,72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-8,03; 13,94</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-8,08; 7,56</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-23,15; 6,76</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.418963728538026</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9433523631170282</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.173000859464989</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-6.70847323979803</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.0382463356398331</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.01914381628083099</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.002655796015867628</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.09287457801446375</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,08</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,64</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-6,95</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-2,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-8,93%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.46773523828878</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.119163350276904</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.520090767258726</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-17.12376698634073</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.03729390741435168</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.0803490079743039</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.08084459183876137</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2314947453793618</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,39; 8,01</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,74; 18,04</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-9,72; 6,84</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-22,0; 11,24</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-9,75; 12,02</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-1,35; 36,64</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-14,61; 11,21</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-26,35; 16,62</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.772235780356422</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.423270207669233</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.733965472853932</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.622866097049587</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1272325050634512</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1393666990855862</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.07563296642975242</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.06759375344243782</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,51</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-5,31</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-0,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-7,24%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.8328697531825302</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>9.082407393299519</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.637233467926091</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-6.954715319439286</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.01159315701779821</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1696305071175258</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.02601092922823361</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.08926746942691728</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,62; 6,47</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,69; 7,61</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 4,05</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-14,2; 3,87</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 10,23</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-1,26; 16,3</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-6,23; 6,63</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-18,36; 5,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.394218472423112</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.7369082983730422</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-9.723067823962095</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-22.00388202638909</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.09751411976729196</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.01349855016326333</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.14608082777502</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2635221230214015</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.006397384044273</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>18.03918228818271</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.840529059047058</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.24189017740404</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1201703489795698</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3664287575028661</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1120796825210275</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1662340068892743</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.506339887559972</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.400795218986069</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.2753724849970163</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-5.313937791468581</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.03835071676113209</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.06925923826742166</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.004280419020507594</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.07242015368393805</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.61501056591531</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.6860700381224329</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.119367065284782</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-14.20344281858877</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.02395720390576664</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.01259958280126782</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.06231859484019749</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1836431515454182</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.469428580667221</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.607713823013556</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.054620270511721</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.872364268931698</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1022833011660444</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.163019501558171</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.06629612987983668</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.05747434705184282</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
